--- a/database.xlsx
+++ b/database.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Changc29\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Changc29\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8721E9D7-447F-4F32-9834-A8C6B9C46968}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F58638B5-1986-4EE4-9EF8-C4ECCD713238}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{53A911C2-308A-40F1-8566-6C4888B57FF2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="3" xr2:uid="{53A911C2-308A-40F1-8566-6C4888B57FF2}"/>
   </bookViews>
   <sheets>
     <sheet name="儀器表" sheetId="2" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7632" uniqueCount="1852">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7634" uniqueCount="1854">
   <si>
     <t>項目名稱</t>
   </si>
@@ -16542,6 +16542,14 @@
   <si>
     <t>BZ3-QP</t>
     <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <t>cobas pro</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cobas pure</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -17096,7 +17104,7 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -17334,6 +17342,9 @@
     </xf>
     <xf numFmtId="49" fontId="17" fillId="3" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -17670,69 +17681,78 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1810241F-B572-4B2A-8EE9-A299C46D8FDB}">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="2" width="16.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="16.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:7">
+      <c r="B1" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
-      <c r="A2" t="s">
+    <row r="2" spans="1:7">
+      <c r="A2" s="80" t="s">
+        <v>1852</v>
+      </c>
+      <c r="B2" t="s">
         <v>311</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>316</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
-      <c r="A3" t="s">
+    <row r="3" spans="1:7">
+      <c r="A3" s="80"/>
+      <c r="B3" t="s">
         <v>312</v>
       </c>
-      <c r="B3" t="s">
+      <c r="D3" s="2" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>1853</v>
+      </c>
+      <c r="B5" t="s">
+        <v>313</v>
+      </c>
+      <c r="C5" t="s">
         <v>317</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" t="s">
-        <v>313</v>
-      </c>
-      <c r="C4" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>356</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="F5" s="2"/>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="F6" s="2"/>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="F7" s="2"/>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="F8" s="2"/>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="F9" s="2"/>
+      <c r="G5" s="2"/>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="G6" s="2"/>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="G7" s="2"/>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="G8" s="2"/>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="G9" s="2"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:A3"/>
+  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -17762,7 +17782,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="B2" t="s">
         <v>204</v>
@@ -17771,12 +17791,12 @@
         <v>2</v>
       </c>
       <c r="D2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>205</v>
@@ -17785,12 +17805,12 @@
         <v>3</v>
       </c>
       <c r="D3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
         <v>206</v>
@@ -17799,12 +17819,12 @@
         <v>4</v>
       </c>
       <c r="D4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
         <v>207</v>
@@ -17813,12 +17833,12 @@
         <v>5</v>
       </c>
       <c r="D5" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
         <v>208</v>
@@ -17827,12 +17847,12 @@
         <v>6</v>
       </c>
       <c r="D6" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="B7" t="s">
         <v>209</v>
@@ -17846,7 +17866,7 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="B8" t="s">
         <v>210</v>
@@ -17860,7 +17880,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="B9" t="s">
         <v>211</v>
@@ -17874,13 +17894,13 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="B10" t="s">
         <v>214</v>
       </c>
       <c r="C10" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D10" t="s">
         <v>225</v>
@@ -17888,105 +17908,105 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="B11" t="s">
         <v>215</v>
       </c>
       <c r="C11" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D11" t="s">
-        <v>229</v>
+        <v>305</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="B12" t="s">
         <v>216</v>
       </c>
       <c r="C12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D12" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="B13" t="s">
         <v>217</v>
       </c>
       <c r="C13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D13" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="B14" t="s">
         <v>218</v>
       </c>
       <c r="C14" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D14" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="B15" t="s">
         <v>219</v>
       </c>
       <c r="C15" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D15" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c r="B16" t="s">
         <v>220</v>
       </c>
       <c r="C16" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D16" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>87</v>
+        <v>52</v>
       </c>
       <c r="B17" t="s">
         <v>221</v>
       </c>
       <c r="C17" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D17" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>90</v>
+        <v>59</v>
       </c>
       <c r="B18" t="s">
         <v>222</v>
@@ -17995,26 +18015,26 @@
         <v>23</v>
       </c>
       <c r="D18" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="B19" t="s">
         <v>223</v>
       </c>
       <c r="C19" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D19" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>108</v>
+        <v>62</v>
       </c>
       <c r="B20" t="s">
         <v>226</v>
@@ -18023,12 +18043,12 @@
         <v>26</v>
       </c>
       <c r="D20" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>109</v>
+        <v>70</v>
       </c>
       <c r="B21" t="s">
         <v>227</v>
@@ -18037,12 +18057,12 @@
         <v>27</v>
       </c>
       <c r="D21" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>113</v>
+        <v>71</v>
       </c>
       <c r="B22" t="s">
         <v>228</v>
@@ -18051,12 +18071,12 @@
         <v>28</v>
       </c>
       <c r="D22" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>117</v>
+        <v>76</v>
       </c>
       <c r="B23" t="s">
         <v>232</v>
@@ -18065,12 +18085,12 @@
         <v>33</v>
       </c>
       <c r="D23" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>122</v>
+        <v>74</v>
       </c>
       <c r="B24" t="s">
         <v>236</v>
@@ -18079,12 +18099,12 @@
         <v>34</v>
       </c>
       <c r="D24" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
       <c r="B25" t="s">
         <v>239</v>
@@ -18093,82 +18113,82 @@
         <v>35</v>
       </c>
       <c r="D25" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>127</v>
+        <v>81</v>
       </c>
       <c r="B26" t="s">
         <v>240</v>
       </c>
       <c r="C26" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D26" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>129</v>
+        <v>84</v>
       </c>
       <c r="B27" t="s">
         <v>243</v>
       </c>
       <c r="C27" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D27" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>137</v>
+        <v>87</v>
       </c>
       <c r="B28" t="s">
         <v>245</v>
       </c>
       <c r="C28" t="s">
-        <v>38</v>
+        <v>196</v>
       </c>
       <c r="D28" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>146</v>
+        <v>90</v>
       </c>
       <c r="B29" t="s">
         <v>247</v>
       </c>
       <c r="C29" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D29" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" t="s">
-        <v>159</v>
+        <v>96</v>
       </c>
       <c r="B30" t="s">
         <v>248</v>
       </c>
       <c r="C30" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D30" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" t="s">
-        <v>167</v>
+        <v>97</v>
       </c>
       <c r="B31" t="s">
         <v>250</v>
@@ -18177,144 +18197,144 @@
         <v>43</v>
       </c>
       <c r="D31" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" t="s">
-        <v>181</v>
+        <v>101</v>
       </c>
       <c r="B32" t="s">
         <v>251</v>
       </c>
       <c r="C32" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D32" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" t="s">
-        <v>184</v>
+        <v>104</v>
       </c>
       <c r="B33" t="s">
         <v>255</v>
       </c>
       <c r="C33" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D33" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>187</v>
+        <v>108</v>
       </c>
       <c r="B34" t="s">
         <v>259</v>
       </c>
       <c r="C34" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D34" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" t="s">
-        <v>189</v>
+        <v>109</v>
       </c>
       <c r="B35" t="s">
         <v>263</v>
       </c>
       <c r="C35" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D35" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" t="s">
-        <v>191</v>
+        <v>113</v>
       </c>
       <c r="B36" t="s">
         <v>264</v>
       </c>
       <c r="C36" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D36" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" t="s">
-        <v>29</v>
+        <v>117</v>
       </c>
       <c r="B37" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C37" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D37" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" t="s">
-        <v>30</v>
+        <v>122</v>
       </c>
       <c r="B38" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C38" t="s">
-        <v>53</v>
+        <v>198</v>
       </c>
       <c r="D38" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" t="s">
-        <v>31</v>
+        <v>125</v>
       </c>
       <c r="B39" t="s">
         <v>272</v>
       </c>
       <c r="C39" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D39" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" t="s">
-        <v>50</v>
+        <v>127</v>
       </c>
       <c r="B40" t="s">
         <v>273</v>
       </c>
       <c r="C40" t="s">
-        <v>55</v>
+        <v>197</v>
       </c>
       <c r="D40" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" t="s">
-        <v>51</v>
+        <v>129</v>
       </c>
       <c r="B41" t="s">
         <v>275</v>
       </c>
       <c r="C41" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D41" t="s">
         <v>280</v>
@@ -18322,156 +18342,156 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42" t="s">
-        <v>1</v>
+        <v>137</v>
       </c>
       <c r="B42" t="s">
         <v>276</v>
       </c>
       <c r="C42" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D42" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="B43" t="s">
         <v>278</v>
       </c>
       <c r="C43" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D43" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" t="s">
-        <v>12</v>
+        <v>159</v>
       </c>
       <c r="B44" t="s">
         <v>281</v>
       </c>
       <c r="C44" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D44" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" t="s">
-        <v>71</v>
+        <v>167</v>
       </c>
       <c r="B45" t="s">
         <v>282</v>
       </c>
       <c r="C45" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="D45" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" t="s">
-        <v>77</v>
+        <v>181</v>
       </c>
       <c r="B46" t="s">
         <v>284</v>
       </c>
       <c r="C46" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D46" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" t="s">
-        <v>84</v>
+        <v>182</v>
       </c>
       <c r="B47" t="s">
         <v>288</v>
       </c>
       <c r="C47" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D47" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" t="s">
-        <v>97</v>
+        <v>183</v>
       </c>
       <c r="B48" t="s">
         <v>290</v>
       </c>
       <c r="C48" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D48" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" t="s">
-        <v>101</v>
+        <v>184</v>
       </c>
       <c r="B49" t="s">
         <v>291</v>
       </c>
       <c r="C49" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D49" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" t="s">
-        <v>104</v>
+        <v>187</v>
       </c>
       <c r="B50" t="s">
         <v>293</v>
       </c>
       <c r="C50" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D50" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="B51" t="s">
         <v>298</v>
       </c>
       <c r="C51" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="D51" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="B52" t="s">
         <v>300</v>
       </c>
       <c r="C52" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="D52" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -18479,10 +18499,10 @@
         <v>301</v>
       </c>
       <c r="C53" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="D53" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -18490,10 +18510,10 @@
         <v>303</v>
       </c>
       <c r="C54" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="D54" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -18501,10 +18521,7 @@
         <v>304</v>
       </c>
       <c r="C55" t="s">
-        <v>78</v>
-      </c>
-      <c r="D55" t="s">
-        <v>289</v>
+        <v>72</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -18512,491 +18529,473 @@
         <v>306</v>
       </c>
       <c r="C56" t="s">
-        <v>79</v>
-      </c>
-      <c r="D56" t="s">
-        <v>292</v>
+        <v>73</v>
       </c>
     </row>
     <row r="57" spans="1:4">
       <c r="C57" t="s">
-        <v>80</v>
-      </c>
-      <c r="D57" t="s">
-        <v>294</v>
+        <v>75</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="C58" t="s">
-        <v>82</v>
-      </c>
-      <c r="D58" t="s">
-        <v>295</v>
+        <v>78</v>
       </c>
     </row>
     <row r="59" spans="1:4">
       <c r="C59" t="s">
-        <v>83</v>
-      </c>
-      <c r="D59" t="s">
-        <v>296</v>
+        <v>79</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="C60" t="s">
-        <v>85</v>
-      </c>
-      <c r="D60" t="s">
-        <v>299</v>
+        <v>80</v>
       </c>
     </row>
     <row r="61" spans="1:4">
       <c r="C61" t="s">
-        <v>86</v>
-      </c>
-      <c r="D61" t="s">
-        <v>302</v>
+        <v>82</v>
       </c>
     </row>
     <row r="62" spans="1:4">
       <c r="C62" t="s">
-        <v>88</v>
-      </c>
-      <c r="D62" t="s">
-        <v>305</v>
+        <v>83</v>
       </c>
     </row>
     <row r="63" spans="1:4">
       <c r="C63" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="64" spans="1:4">
       <c r="C64" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
     </row>
     <row r="65" spans="3:3">
       <c r="C65" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="66" spans="3:3">
       <c r="C66" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
     </row>
     <row r="67" spans="3:3">
       <c r="C67" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="68" spans="3:3">
       <c r="C68" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="69" spans="3:3">
       <c r="C69" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="70" spans="3:3">
       <c r="C70" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
     </row>
     <row r="71" spans="3:3">
       <c r="C71" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="72" spans="3:3">
       <c r="C72" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="73" spans="3:3">
       <c r="C73" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="74" spans="3:3">
       <c r="C74" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
     </row>
     <row r="75" spans="3:3">
       <c r="C75" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="76" spans="3:3">
       <c r="C76" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="77" spans="3:3">
       <c r="C77" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
     </row>
     <row r="78" spans="3:3">
       <c r="C78" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
     </row>
     <row r="79" spans="3:3">
       <c r="C79" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="80" spans="3:3">
       <c r="C80" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="81" spans="3:3">
       <c r="C81" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="82" spans="3:3">
       <c r="C82" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
     </row>
     <row r="83" spans="3:3">
       <c r="C83" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="84" spans="3:3">
       <c r="C84" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="85" spans="3:3">
       <c r="C85" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
     </row>
     <row r="86" spans="3:3">
       <c r="C86" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="87" spans="3:3">
       <c r="C87" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="88" spans="3:3">
       <c r="C88" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
     </row>
     <row r="89" spans="3:3">
       <c r="C89" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
     </row>
     <row r="90" spans="3:3">
       <c r="C90" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
     </row>
     <row r="91" spans="3:3">
       <c r="C91" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
     </row>
     <row r="92" spans="3:3">
       <c r="C92" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
     </row>
     <row r="93" spans="3:3">
       <c r="C93" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="94" spans="3:3">
       <c r="C94" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="95" spans="3:3">
       <c r="C95" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="96" spans="3:3">
       <c r="C96" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="97" spans="3:3">
       <c r="C97" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="98" spans="3:3">
       <c r="C98" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="99" spans="3:3">
       <c r="C99" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="100" spans="3:3">
       <c r="C100" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="101" spans="3:3">
       <c r="C101" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="102" spans="3:3">
       <c r="C102" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="103" spans="3:3">
       <c r="C103" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="104" spans="3:3">
       <c r="C104" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="105" spans="3:3">
       <c r="C105" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="106" spans="3:3">
       <c r="C106" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="107" spans="3:3">
       <c r="C107" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
     </row>
     <row r="108" spans="3:3">
       <c r="C108" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="109" spans="3:3">
       <c r="C109" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="110" spans="3:3">
       <c r="C110" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="111" spans="3:3">
       <c r="C111" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="112" spans="3:3">
       <c r="C112" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="113" spans="3:3">
       <c r="C113" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="114" spans="3:3">
       <c r="C114" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="115" spans="3:3">
       <c r="C115" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
     </row>
     <row r="116" spans="3:3">
       <c r="C116" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
     </row>
     <row r="117" spans="3:3">
       <c r="C117" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="118" spans="3:3">
       <c r="C118" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
     </row>
     <row r="119" spans="3:3">
       <c r="C119" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
     </row>
     <row r="120" spans="3:3">
       <c r="C120" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
     </row>
     <row r="121" spans="3:3">
       <c r="C121" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
     <row r="122" spans="3:3">
       <c r="C122" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="123" spans="3:3">
       <c r="C123" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="124" spans="3:3">
       <c r="C124" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
     </row>
     <row r="125" spans="3:3">
       <c r="C125" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="126" spans="3:3">
       <c r="C126" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
     </row>
     <row r="127" spans="3:3">
       <c r="C127" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="128" spans="3:3">
       <c r="C128" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="129" spans="3:3">
       <c r="C129" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="130" spans="3:3">
       <c r="C130" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="131" spans="3:3">
       <c r="C131" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
     <row r="132" spans="3:3">
       <c r="C132" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
     </row>
     <row r="133" spans="3:3">
       <c r="C133" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="134" spans="3:3">
       <c r="C134" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="135" spans="3:3">
       <c r="C135" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
     <row r="136" spans="3:3">
       <c r="C136" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
     </row>
     <row r="137" spans="3:3">
       <c r="C137" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
     </row>
     <row r="138" spans="3:3">
       <c r="C138" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
     </row>
     <row r="139" spans="3:3">
       <c r="C139" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
     </row>
     <row r="140" spans="3:3">
       <c r="C140" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
     </row>
     <row r="141" spans="3:3">
       <c r="C141" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
     </row>
     <row r="142" spans="3:3">
       <c r="C142" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
     </row>
     <row r="143" spans="3:3">
       <c r="C143" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
     </row>
     <row r="144" spans="3:3">
       <c r="C144" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="145" spans="3:3">
       <c r="C145" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
     <row r="146" spans="3:3">
       <c r="C146" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="147" spans="3:3">
       <c r="C147" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="148" spans="3:3">
       <c r="C148" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="D2:D152">
+    <sortCondition ref="D2:D152"/>
+  </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -19030,25 +19029,49 @@
       <c r="A1" s="2" t="s">
         <v>311</v>
       </c>
+      <c r="B1" s="2" t="s">
+        <v>311</v>
+      </c>
       <c r="C1" s="2" t="s">
         <v>312</v>
       </c>
+      <c r="D1" s="2" t="s">
+        <v>312</v>
+      </c>
       <c r="E1" s="2" t="s">
         <v>313</v>
       </c>
+      <c r="F1" s="2" t="s">
+        <v>313</v>
+      </c>
       <c r="G1" s="2" t="s">
         <v>316</v>
       </c>
+      <c r="H1" s="2" t="s">
+        <v>316</v>
+      </c>
       <c r="I1" s="2" t="s">
         <v>317</v>
       </c>
+      <c r="J1" s="2" t="s">
+        <v>317</v>
+      </c>
       <c r="K1" s="2" t="s">
         <v>318</v>
       </c>
+      <c r="L1" s="2" t="s">
+        <v>318</v>
+      </c>
       <c r="M1" s="2" t="s">
         <v>329</v>
       </c>
+      <c r="N1" s="2" t="s">
+        <v>329</v>
+      </c>
       <c r="O1" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="P1" s="2" t="s">
         <v>356</v>
       </c>
     </row>
@@ -19407,7 +19430,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O19" xr:uid="{4478D013-B584-444B-8DAB-8BB82D1C358E}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/database.xlsx
+++ b/database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Changc29\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FB51657-BA5B-480C-88F5-BA7855F2FEAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF6F41CE-83D9-4EF1-A64F-537C49B6C65F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="4" xr2:uid="{53A911C2-308A-40F1-8566-6C4888B57FF2}"/>
   </bookViews>
@@ -16546,22 +16546,6 @@
     <t>cobas c pack MULTI opening tool</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">100 pc/pack </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="細明體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>量很大，倉庫有，若真的需要再申請</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>50 pc</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -16699,21 +16683,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>5000P</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Imago"/>
-        <family val="2"/>
-      </rPr>
-      <t>，量很大，倉庫有，若真的需要再申請</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>貨號</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -16743,6 +16712,38 @@
   </si>
   <si>
     <t>10 pc，請確認工程師是否已申請</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">100 pc/pack </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>倉庫有，需要再申請</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">5000P </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>倉庫有，需要再申請</t>
+    </r>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -16750,7 +16751,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="39">
+  <fonts count="40">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -17003,6 +17004,13 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Microsoft JhengHei UI"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微軟正黑體"/>
       <family val="2"/>
       <charset val="136"/>
     </font>
@@ -50053,13 +50061,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="96" t="s">
+        <v>1882</v>
+      </c>
+      <c r="B1" s="96" t="s">
+        <v>1883</v>
+      </c>
+      <c r="C1" s="97" t="s">
         <v>1884</v>
-      </c>
-      <c r="B1" s="96" t="s">
-        <v>1885</v>
-      </c>
-      <c r="C1" s="97" t="s">
-        <v>1886</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -50070,7 +50078,7 @@
         <v>1807</v>
       </c>
       <c r="C2" s="95" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -50081,7 +50089,7 @@
         <v>1809</v>
       </c>
       <c r="C3" s="95" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -50103,7 +50111,7 @@
         <v>1811</v>
       </c>
       <c r="C5" s="95" t="s">
-        <v>1863</v>
+        <v>1862</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -50125,7 +50133,7 @@
         <v>1813</v>
       </c>
       <c r="C7" s="95" t="s">
-        <v>1864</v>
+        <v>1863</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -50147,7 +50155,7 @@
         <v>1815</v>
       </c>
       <c r="C9" s="95" t="s">
-        <v>1887</v>
+        <v>1885</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -50169,7 +50177,7 @@
         <v>1817</v>
       </c>
       <c r="C11" s="95" t="s">
-        <v>1864</v>
+        <v>1863</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -50191,7 +50199,7 @@
         <v>1819</v>
       </c>
       <c r="C13" s="95" t="s">
-        <v>1865</v>
+        <v>1864</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -50213,7 +50221,7 @@
         <v>1821</v>
       </c>
       <c r="C15" s="95" t="s">
-        <v>1866</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -50235,7 +50243,7 @@
         <v>1823</v>
       </c>
       <c r="C17" s="95" t="s">
-        <v>1865</v>
+        <v>1864</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -50257,7 +50265,7 @@
         <v>1825</v>
       </c>
       <c r="C19" s="95" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -50279,7 +50287,7 @@
         <v>1827</v>
       </c>
       <c r="C21" s="95" t="s">
-        <v>1868</v>
+        <v>1867</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -50301,7 +50309,7 @@
         <v>1829</v>
       </c>
       <c r="C23" s="95" t="s">
-        <v>1869</v>
+        <v>1868</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -50323,7 +50331,7 @@
         <v>1831</v>
       </c>
       <c r="C25" s="95" t="s">
-        <v>1888</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -50345,7 +50353,7 @@
         <v>1833</v>
       </c>
       <c r="C27" s="95" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -50367,7 +50375,7 @@
         <v>1835</v>
       </c>
       <c r="C29" s="95" t="s">
-        <v>1870</v>
+        <v>1869</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -50389,7 +50397,7 @@
         <v>1837</v>
       </c>
       <c r="C31" s="95" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -50411,18 +50419,18 @@
         <v>1839</v>
       </c>
       <c r="C33" s="95" t="s">
-        <v>1872</v>
+        <v>1871</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="95" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
       <c r="B34" s="95" t="s">
         <v>1845</v>
       </c>
       <c r="C34" s="95" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -50433,7 +50441,7 @@
         <v>1846</v>
       </c>
       <c r="C35" s="95" t="s">
-        <v>1881</v>
+        <v>1880</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -50444,29 +50452,29 @@
         <v>1847</v>
       </c>
       <c r="C36" s="95" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="95" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
       <c r="B37" s="95" t="s">
         <v>1848</v>
       </c>
       <c r="C37" s="95" t="s">
-        <v>1882</v>
+        <v>1881</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="95" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
       <c r="B38" s="95" t="s">
         <v>1849</v>
       </c>
       <c r="C38" s="95" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -50477,7 +50485,7 @@
         <v>1850</v>
       </c>
       <c r="C39" s="95" t="s">
-        <v>1881</v>
+        <v>1880</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -50488,29 +50496,29 @@
         <v>1851</v>
       </c>
       <c r="C40" s="95" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="95" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
       <c r="B41" s="95" t="s">
         <v>1852</v>
       </c>
       <c r="C41" s="95" t="s">
-        <v>1882</v>
+        <v>1881</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="95" t="s">
-        <v>1877</v>
+        <v>1876</v>
       </c>
       <c r="B42" s="95" t="s">
         <v>1853</v>
       </c>
       <c r="C42" s="95" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -50521,7 +50529,7 @@
         <v>1854</v>
       </c>
       <c r="C43" s="95" t="s">
-        <v>1881</v>
+        <v>1880</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -50532,7 +50540,7 @@
         <v>1861</v>
       </c>
       <c r="C44" s="95" t="s">
-        <v>1862</v>
+        <v>1887</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -50543,7 +50551,7 @@
         <v>1805</v>
       </c>
       <c r="C45" s="95" t="s">
-        <v>1883</v>
+        <v>1888</v>
       </c>
     </row>
   </sheetData>

--- a/database.xlsx
+++ b/database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Changc29\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF6F41CE-83D9-4EF1-A64F-537C49B6C65F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECD87DDA-9C2D-4886-8291-DBD9A3BA8923}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="4" xr2:uid="{53A911C2-308A-40F1-8566-6C4888B57FF2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{53A911C2-308A-40F1-8566-6C4888B57FF2}"/>
   </bookViews>
   <sheets>
     <sheet name="儀器表" sheetId="2" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7446" uniqueCount="1889">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7446" uniqueCount="1891">
   <si>
     <t>A1MGU</t>
   </si>
@@ -16745,6 +16745,14 @@
       <t>倉庫有，需要再申請</t>
     </r>
     <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>cobas pro   c 703</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cobas pro   c 503</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -18048,7 +18056,7 @@
         <v>1716</v>
       </c>
       <c r="B2" t="s">
-        <v>271</v>
+        <v>1889</v>
       </c>
       <c r="C2" t="s">
         <v>276</v>
@@ -18060,7 +18068,7 @@
     <row r="3" spans="1:7">
       <c r="A3" s="98"/>
       <c r="B3" t="s">
-        <v>272</v>
+        <v>1890</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>289</v>

--- a/database.xlsx
+++ b/database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Changc29\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECD87DDA-9C2D-4886-8291-DBD9A3BA8923}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12890D61-F287-494E-B199-0BB59C5C0EC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{53A911C2-308A-40F1-8566-6C4888B57FF2}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7446" uniqueCount="1891">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7446" uniqueCount="1889">
   <si>
     <t>A1MGU</t>
   </si>
@@ -16745,14 +16745,6 @@
       <t>倉庫有，需要再申請</t>
     </r>
     <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>cobas pro   c 703</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>cobas pro   c 503</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -18056,7 +18048,7 @@
         <v>1716</v>
       </c>
       <c r="B2" t="s">
-        <v>1889</v>
+        <v>271</v>
       </c>
       <c r="C2" t="s">
         <v>276</v>
@@ -18068,7 +18060,7 @@
     <row r="3" spans="1:7">
       <c r="A3" s="98"/>
       <c r="B3" t="s">
-        <v>1890</v>
+        <v>272</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>289</v>
